--- a/artfynd/A 31199-2023 artfynd.xlsx
+++ b/artfynd/A 31199-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31199-2023 artfynd.xlsx
+++ b/artfynd/A 31199-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133850760</v>
       </c>
       <c r="B2" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>133851038</v>
       </c>
       <c r="B4" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>133850866</v>
       </c>
       <c r="B35" t="n">
-        <v>83342</v>
+        <v>83349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>133851070</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>133851017</v>
       </c>
       <c r="B37" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>133850936</v>
       </c>
       <c r="B38" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 31199-2023 artfynd.xlsx
+++ b/artfynd/A 31199-2023 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133850760</v>
+        <v>119022577</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574367</v>
+        <v>574396</v>
       </c>
       <c r="R2" t="n">
-        <v>7205955</v>
+        <v>7205913</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-65</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,68 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96592370</v>
+        <v>133851017</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hiberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574340.9369898803</v>
+        <v>574397</v>
       </c>
       <c r="R3" t="n">
-        <v>7205977.278331227</v>
+        <v>7205914</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,29 +866,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133851038</v>
+        <v>119022576</v>
       </c>
       <c r="B4" t="n">
-        <v>91987</v>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,33 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574454</v>
+        <v>574407</v>
       </c>
       <c r="R4" t="n">
-        <v>7205865</v>
+        <v>7205918</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,17 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,71 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115413297</v>
+        <v>119022584</v>
       </c>
       <c r="B5" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574344</v>
+        <v>574454</v>
       </c>
       <c r="R5" t="n">
-        <v>7205965</v>
+        <v>7205926</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1070,22 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115417683</v>
+        <v>96592386</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,34 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Hiberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574460</v>
+        <v>574367</v>
       </c>
       <c r="R6" t="n">
-        <v>7205929</v>
+        <v>7205956</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:41</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,71 +1180,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115417732</v>
+        <v>133850760</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574264</v>
+        <v>574367</v>
       </c>
       <c r="R7" t="n">
-        <v>7205842</v>
+        <v>7205955</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,22 +1264,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-65</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,67 +1289,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115413264</v>
+        <v>115417728</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574240</v>
+        <v>574458</v>
       </c>
       <c r="R8" t="n">
-        <v>7205804</v>
+        <v>7205932</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1416,7 +1371,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1381,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,19 +1408,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115417728</v>
+        <v>115417729</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1493,7 +1443,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574458</v>
+        <v>574398</v>
       </c>
       <c r="R9" t="n">
         <v>7205932</v>
@@ -1528,7 +1478,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1488,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,19 +1515,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115417733</v>
+        <v>115417730</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1605,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574243</v>
+        <v>574335</v>
       </c>
       <c r="R10" t="n">
-        <v>7205803</v>
+        <v>7205937</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1640,7 +1585,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1595,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,16 +1625,11 @@
         <v>115417731</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1789,19 +1729,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115417729</v>
+        <v>115417732</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1829,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574398</v>
+        <v>574264</v>
       </c>
       <c r="R12" t="n">
-        <v>7205932</v>
+        <v>7205842</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1799,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1809,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,19 +1836,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115417730</v>
+        <v>115417733</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1941,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574335</v>
+        <v>574243</v>
       </c>
       <c r="R13" t="n">
-        <v>7205937</v>
+        <v>7205803</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1976,7 +1906,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1916,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,37 +1943,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115413307</v>
+        <v>119022569</v>
       </c>
       <c r="B14" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574270</v>
+        <v>574504</v>
       </c>
       <c r="R14" t="n">
-        <v>7205874</v>
+        <v>7205817</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2083,22 +2008,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,37 +2050,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115417703</v>
+        <v>119022571</v>
       </c>
       <c r="B15" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574398</v>
+        <v>574259</v>
       </c>
       <c r="R15" t="n">
-        <v>7205932</v>
+        <v>7205903</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2195,22 +2115,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,55 +2157,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115413263</v>
+        <v>119022573</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574265</v>
+        <v>574374</v>
       </c>
       <c r="R16" t="n">
-        <v>7205847</v>
+        <v>7205910</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2312,22 +2222,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,37 +2264,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119022577</v>
+        <v>119022578</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,7 +2299,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574396</v>
+        <v>574397</v>
       </c>
       <c r="R17" t="n">
         <v>7205913</v>
@@ -2466,19 +2371,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119022588</v>
+        <v>119022581</v>
       </c>
       <c r="B18" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2506,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574493</v>
+        <v>574410</v>
       </c>
       <c r="R18" t="n">
-        <v>7205926</v>
+        <v>7205920</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2541,7 +2441,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,7 +2451,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,37 +2478,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119022576</v>
+        <v>119022588</v>
       </c>
       <c r="B19" t="n">
-        <v>74628</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2618,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574407</v>
+        <v>574493</v>
       </c>
       <c r="R19" t="n">
-        <v>7205918</v>
+        <v>7205926</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2653,7 +2548,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,7 +2558,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,19 +2585,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119022573</v>
+        <v>133851070</v>
       </c>
       <c r="B20" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2726,17 +2616,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574374</v>
+        <v>574334</v>
       </c>
       <c r="R20" t="n">
-        <v>7205910</v>
+        <v>7205938</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,22 +2650,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,27 +2675,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119022583</v>
+        <v>96592370</v>
       </c>
       <c r="B21" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,16 +2716,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Hiberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574443</v>
+        <v>574341</v>
       </c>
       <c r="R21" t="n">
-        <v>7205914</v>
+        <v>7205977</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2872,22 +2755,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,55 +2769,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119022584</v>
+        <v>119022583</v>
       </c>
       <c r="B22" t="n">
-        <v>94280</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2954,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574454</v>
+        <v>574443</v>
       </c>
       <c r="R22" t="n">
-        <v>7205926</v>
+        <v>7205914</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2989,7 +2858,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2999,7 +2868,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,37 +2895,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119022572</v>
+        <v>119022574</v>
       </c>
       <c r="B23" t="n">
-        <v>79621</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574374</v>
+        <v>574370</v>
       </c>
       <c r="R23" t="n">
-        <v>7205910</v>
+        <v>7205924</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,7 +2965,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3111,7 +2975,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,15 +3002,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119022578</v>
+        <v>133850936</v>
       </c>
       <c r="B24" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,37 +3013,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574397</v>
+        <v>574371</v>
       </c>
       <c r="R24" t="n">
-        <v>7205913</v>
+        <v>7205929</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,22 +3067,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På rönn.  Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3238,49 +3092,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119022581</v>
+        <v>115413307</v>
       </c>
       <c r="B25" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3290,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574410</v>
+        <v>574270</v>
       </c>
       <c r="R25" t="n">
-        <v>7205920</v>
+        <v>7205874</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3320,22 +3169,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,37 +3211,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119022571</v>
+        <v>119022572</v>
       </c>
       <c r="B26" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574259</v>
+        <v>574374</v>
       </c>
       <c r="R26" t="n">
-        <v>7205903</v>
+        <v>7205910</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3437,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3447,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,32 +3318,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119022569</v>
+        <v>119022585</v>
       </c>
       <c r="B27" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3514,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574504</v>
+        <v>574454</v>
       </c>
       <c r="R27" t="n">
-        <v>7205817</v>
+        <v>7205925</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3549,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,15 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119022587</v>
+        <v>115417683</v>
       </c>
       <c r="B28" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,21 +3436,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574473</v>
+        <v>574460</v>
       </c>
       <c r="R28" t="n">
-        <v>7205926</v>
+        <v>7205929</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3656,22 +3490,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,12 +3535,7 @@
         <v>119022575</v>
       </c>
       <c r="B29" t="n">
-        <v>79628</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3810,15 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119022585</v>
+        <v>119022579</v>
       </c>
       <c r="B30" t="n">
-        <v>79627</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3826,21 +3650,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3850,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574454</v>
+        <v>574407</v>
       </c>
       <c r="R30" t="n">
-        <v>7205925</v>
+        <v>7205917</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3885,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3895,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,37 +3746,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119022574</v>
+        <v>119022586</v>
       </c>
       <c r="B31" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6486</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3962,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574370</v>
+        <v>574473</v>
       </c>
       <c r="R31" t="n">
-        <v>7205924</v>
+        <v>7205930</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3997,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4007,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4034,53 +3853,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119022582</v>
+        <v>133850866</v>
       </c>
       <c r="B32" t="n">
-        <v>77448</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574450</v>
+        <v>574483</v>
       </c>
       <c r="R32" t="n">
-        <v>7205918</v>
+        <v>7205936</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4104,22 +3918,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-60</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,62 +3943,62 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119022586</v>
+        <v>115413263</v>
       </c>
       <c r="B33" t="n">
-        <v>74621</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574473</v>
+        <v>574265</v>
       </c>
       <c r="R33" t="n">
-        <v>7205930</v>
+        <v>7205847</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4216,22 +4025,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4258,50 +4067,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119022579</v>
+        <v>115413264</v>
       </c>
       <c r="B34" t="n">
-        <v>79628</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574407</v>
+        <v>574240</v>
       </c>
       <c r="R34" t="n">
-        <v>7205917</v>
+        <v>7205804</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4328,22 +4137,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4370,48 +4179,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133850866</v>
+        <v>115413265</v>
       </c>
       <c r="B35" t="n">
-        <v>83349</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574483</v>
+        <v>574206</v>
       </c>
       <c r="R35" t="n">
-        <v>7205936</v>
+        <v>7205721</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4435,17 +4249,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-60</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,22 +4279,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133851070</v>
+        <v>115413297</v>
       </c>
       <c r="B36" t="n">
-        <v>79366</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,37 +4302,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574334</v>
+        <v>574344</v>
       </c>
       <c r="R36" t="n">
-        <v>7205938</v>
+        <v>7205965</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,17 +4365,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-75</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4562,60 +4395,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133851017</v>
+        <v>119022587</v>
       </c>
       <c r="B37" t="n">
-        <v>91981</v>
+        <v>97983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574397</v>
+        <v>574473</v>
       </c>
       <c r="R37" t="n">
-        <v>7205914</v>
+        <v>7205926</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4639,17 +4472,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-56</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4664,22 +4502,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133850936</v>
+        <v>119022582</v>
       </c>
       <c r="B38" t="n">
-        <v>80481</v>
+        <v>78339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4687,37 +4525,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574371</v>
+        <v>574450</v>
       </c>
       <c r="R38" t="n">
-        <v>7205929</v>
+        <v>7205918</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4741,17 +4579,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På rönn.  Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4766,12 +4609,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 31199-2023 artfynd.xlsx
+++ b/artfynd/A 31199-2023 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>574397</v>
       </c>
       <c r="R3" t="n">
-        <v>7205914</v>
+        <v>7205913</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31199-2023 artfynd.xlsx
+++ b/artfynd/A 31199-2023 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>574397</v>
       </c>
       <c r="R3" t="n">
-        <v>7205913</v>
+        <v>7205914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
